--- a/artfynd/A 44116-2022 artfynd.xlsx
+++ b/artfynd/A 44116-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44116-2022 artfynd.xlsx
+++ b/artfynd/A 44116-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109909947</v>
+        <v>112610378</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513117.3709834392</v>
+        <v>513118</v>
       </c>
       <c r="R2" t="n">
-        <v>6851073.896923918</v>
+        <v>6851074</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112610378</v>
+        <v>112610402</v>
       </c>
       <c r="B3" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513117</v>
+        <v>513844</v>
       </c>
       <c r="R3" t="n">
-        <v>6851074</v>
+        <v>6850689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 44116-2022 artfynd.xlsx
+++ b/artfynd/A 44116-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>